--- a/Result/profitability/5364.xlsx
+++ b/Result/profitability/5364.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1875</v>
+        <v>-0.135</v>
       </c>
       <c r="N2" t="n">
-        <v>11.24625</v>
+        <v>10.2025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.16375</v>
+        <v>-0.20625</v>
       </c>
       <c r="N3" t="n">
-        <v>12.805</v>
+        <v>8.253749999999998</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.205</v>
+        <v>-0.18875</v>
       </c>
       <c r="N4" t="n">
-        <v>10.12875</v>
+        <v>8.428749999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.665</v>
+        <v>-0.6525</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5762500000000017</v>
+        <v>-3.282500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.72375</v>
+        <v>-0.7324999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.611250000000001</v>
+        <v>-7.93125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.76125</v>
+        <v>-0.7787499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.836250000000001</v>
+        <v>-10.94</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>-0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.855</v>
+        <v>-0.8612500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.71125</v>
+        <v>-14.27125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5364</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-14.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-92.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.19625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.554999999999998</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-28.48</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.027046263345196</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3448275862068965</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-21.65</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-2.998614958448754</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
